--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1593-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1593-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{575C5E96-7739-46DF-9F20-3BA62647C66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C72C1857-9AFC-4562-B32F-AC6F0F536346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F12D77E6-3537-40DA-B92B-B3043D4A67F5}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{19CCDA7C-598C-4613-81F7-1F46102740E9}"/>
   </bookViews>
   <sheets>
     <sheet name="1593-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1466,23 +1466,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494F0E25-EEF2-40B6-A392-5A3D693D1CAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E5893AF-DB37-48AC-BCAA-091765AF4FF2}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1509,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1540,7 +1539,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1586,7 +1585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1636,7 +1635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1690,7 +1689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1746,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1912,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1968,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2024</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2190,7 +2189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2358,7 +2357,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2023</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2524,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2022</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2021</v>
       </c>
@@ -2744,7 +2743,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2020</v>
       </c>
@@ -2798,7 +2797,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2019</v>
       </c>
@@ -2852,7 +2851,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2018</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2017</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2016</v>
       </c>
@@ -3014,7 +3013,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2015</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2014</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2013</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2012</v>
       </c>
@@ -3230,7 +3229,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2011</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
         <v>41</v>
       </c>
